--- a/fixtures/text/excel_basic.xlsx
+++ b/fixtures/text/excel_basic.xlsx
@@ -461,12 +461,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Model No.</t>
+          <t>Body Model(Type)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>667-ED</t>
+          <t>657-ED(GLOBE)</t>
         </is>
       </c>
     </row>
@@ -515,6 +515,18 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>4 IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Max Shutoff / Shutoff Class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>120 psi / ANSI IV</t>
         </is>
       </c>
     </row>
